--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486885_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486885_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. TRAORE</t>
+          <t>D. JACKSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3562</v>
+        <v>2.1367</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8387</v>
+        <v>4.1228</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.4824</v>
+        <v>-1.9861</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.808</v>
+        <v>2.5143</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0317</v>
+        <v>3.5719</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7763</v>
+        <v>-1.0575</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0744</v>
+        <v>5.9362</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2988</v>
+        <v>5.7653</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7756</v>
+        <v>0.1709</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.8824</v>
+        <v>-3.4219</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3305</v>
+        <v>-2.1934</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.5519</v>
+        <v>-1.2284</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4107</v>
+        <v>1.6427</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4374</v>
+        <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2176</v>
+        <v>-0.6015</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7746</v>
+        <v>-0.7867</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.1852</v>
       </c>
       <c r="V2" t="n">
-        <v>3.5359</v>
+        <v>-1.4189</v>
       </c>
       <c r="W2" t="n">
-        <v>4.0164</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4805</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. JACKSON</t>
+          <t>J. SÁNCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2164</v>
+        <v>1.7158</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4021</v>
+        <v>4.2347</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1857</v>
+        <v>-2.5189</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5143</v>
+        <v>3.1201</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5719</v>
+        <v>1.2944</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0575</v>
+        <v>1.8258</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9362</v>
+        <v>4.8352</v>
       </c>
       <c r="K3" t="n">
-        <v>5.7653</v>
+        <v>1.8492</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1709</v>
+        <v>2.986</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.4219</v>
+        <v>-1.7151</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.1934</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2284</v>
+        <v>-1.1602</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6427</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6694</v>
+        <v>0.616</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5218</v>
+        <v>0.6654</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5073</v>
+        <v>0.4261</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9856</v>
+        <v>0.2393</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4189</v>
+        <v>-1.6591</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4189</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SÁNCHEZ</t>
+          <t>B. TRAORE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2677</v>
+        <v>1.3966</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8163</v>
+        <v>4.8198</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.5485</v>
+        <v>-3.4232</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1201</v>
+        <v>-1.808</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2944</v>
+        <v>-1.0317</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8258</v>
+        <v>-0.7763</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8352</v>
+        <v>2.0744</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8492</v>
+        <v>0.2988</v>
       </c>
       <c r="L4" t="n">
-        <v>2.986</v>
+        <v>1.7756</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7151</v>
+        <v>-3.8824</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-1.3305</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1602</v>
+        <v>-2.5519</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4107</v>
+        <v>0.4107</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2174</v>
+        <v>-0.742</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0077</v>
+        <v>-0.2443</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2097</v>
+        <v>-0.4977</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6591</v>
+        <v>3.5359</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.0164</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6591</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MOURE COLOMBO</t>
+          <t>E. MARTINEZ PRETEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9692</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7052</v>
+        <v>5.0498</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7873</v>
+        <v>-4.0807</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6114</v>
+        <v>1.6395</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0512</v>
+        <v>-0.8599</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5602</v>
+        <v>2.4994</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0612</v>
+        <v>4.1379</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2458</v>
+        <v>0.6653</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8154</v>
+        <v>3.4726</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4498</v>
+        <v>-2.4984</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1947</v>
+        <v>-1.5252</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2552</v>
+        <v>-0.9732</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3096</v>
+        <v>-1.3212</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3294</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0198</v>
+        <v>-0.6624</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.5975</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1786</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. MARTINEZ PRETEL</t>
+          <t>E. MOURE COLOMBO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5205</v>
+        <v>0.9475</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9568</v>
+        <v>1.7052</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.4364</v>
+        <v>-0.7577</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6395</v>
+        <v>2.6114</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8599</v>
+        <v>1.0512</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4994</v>
+        <v>1.5602</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1379</v>
+        <v>3.0612</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6653</v>
+        <v>1.2458</v>
       </c>
       <c r="L6" t="n">
-        <v>3.4726</v>
+        <v>1.8154</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4984</v>
+        <v>-0.4498</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5252</v>
+        <v>-0.1947</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9732</v>
+        <v>-0.2552</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7699</v>
+        <v>-0.28</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7518</v>
+        <v>-0.3294</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0181</v>
+        <v>0.0494</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2402</v>
+        <v>-1.1786</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5975</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3573</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2497</v>
+        <v>-1.2793</v>
       </c>
       <c r="E7" t="n">
         <v>1.2674</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5171</v>
+        <v>-2.5467</v>
       </c>
       <c r="G7" t="n">
         <v>-0.06370000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8675</v>
+        <v>0.8378</v>
       </c>
       <c r="T7" t="n">
         <v>0.5075</v>
       </c>
       <c r="U7" t="n">
-        <v>0.36</v>
+        <v>0.3304</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7389</v>
+        <v>-1.4704</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1659</v>
+        <v>-0.9567</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5729</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4824</v>
@@ -1078,13 +1078,13 @@
         <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1131</v>
+        <v>0.3816</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0736</v>
+        <v>0.2828</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0395</v>
+        <v>0.0988</v>
       </c>
       <c r="V8" t="n">
         <v>-1.9856</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7278</v>
+        <v>-3.443</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4804</v>
+        <v>-1.492</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2474</v>
+        <v>-1.951</v>
       </c>
       <c r="G9" t="n">
         <v>-1.692</v>
@@ -1156,13 +1156,13 @@
         <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9804</v>
+        <v>-0.6955</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6201</v>
+        <v>-0.6317</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3603</v>
+        <v>-0.0638</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8768</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2521</v>
+        <v>-3.8881</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8054</v>
+        <v>-0.5303</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4467</v>
+        <v>-3.3577</v>
       </c>
       <c r="G10" t="n">
         <v>-3.8463</v>
@@ -1234,13 +1234,13 @@
         <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5413</v>
+        <v>-0.1773</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.283</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2583</v>
+        <v>-0.1694</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4805</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.659000000000001</v>
+        <v>-8.4457</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3997</v>
+        <v>-4.0975</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.2592</v>
+        <v>-4.3482</v>
       </c>
       <c r="G11" t="n">
         <v>-4.8744</v>
@@ -1312,13 +1312,13 @@
         <v>2.2588</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2836</v>
+        <v>-1.0703</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1471</v>
+        <v>-0.8448</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1365</v>
+        <v>-0.2255</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7063</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.3489</v>
+        <v>-11.3607</v>
       </c>
       <c r="E12" t="n">
-        <v>13.1351</v>
+        <v>14.1232</v>
       </c>
       <c r="F12" t="n">
-        <v>-25.4836</v>
+        <v>-25.4838</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8815</v>
@@ -1366,7 +1366,7 @@
         <v>20.4353</v>
       </c>
       <c r="K12" t="n">
-        <v>6.637499999999999</v>
+        <v>6.637500000000001</v>
       </c>
       <c r="L12" t="n">
         <v>13.7978</v>
@@ -1390,13 +1390,13 @@
         <v>14.3739</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.991000000000001</v>
+        <v>-3.003</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.2753</v>
+        <v>-2.2872</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7156</v>
+        <v>-0.7156999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-7.5297</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5501</v>
+        <v>6.2659</v>
       </c>
       <c r="E13" t="n">
-        <v>8.315099999999999</v>
+        <v>8.001300000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.765</v>
+        <v>-1.7353</v>
       </c>
       <c r="G13" t="n">
         <v>0.1776</v>
@@ -1468,13 +1468,13 @@
         <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2595</v>
+        <v>0.9754</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8096</v>
+        <v>0.4958</v>
       </c>
       <c r="U13" t="n">
-        <v>0.45</v>
+        <v>0.4796</v>
       </c>
       <c r="V13" t="n">
         <v>4.0862</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3323</v>
+        <v>6.0088</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6534</v>
+        <v>5.0719</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.9369</v>
       </c>
       <c r="G14" t="n">
         <v>0.2829</v>
@@ -1546,13 +1546,13 @@
         <v>2.0534</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2153</v>
+        <v>0.4611</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6433</v>
+        <v>-0.2249</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4279</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>5.2648</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6864</v>
+        <v>4.4998</v>
       </c>
       <c r="E15" t="n">
         <v>4.5653</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1211</v>
+        <v>-0.0655</v>
       </c>
       <c r="G15" t="n">
         <v>3.6889</v>
@@ -1624,13 +1624,13 @@
         <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7552</v>
+        <v>0.5687</v>
       </c>
       <c r="T15" t="n">
         <v>-0.0854</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8406</v>
+        <v>0.654</v>
       </c>
       <c r="V15" t="n">
         <v>2.2957</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ANDREATTA</t>
+          <t>F. STUTZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0493</v>
+        <v>3.3284</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0675</v>
+        <v>4.5954</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0181</v>
+        <v>-1.267</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4368</v>
+        <v>0.1299</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2976</v>
+        <v>2.4426</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1392</v>
+        <v>-2.3128</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5833</v>
+        <v>3.9701</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7943</v>
+        <v>2.826</v>
       </c>
       <c r="L16" t="n">
-        <v>1.789</v>
+        <v>1.1441</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1465</v>
+        <v>-3.8402</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4967</v>
+        <v>-0.3833</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3502</v>
+        <v>-3.4569</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0267</v>
+        <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9431</v>
+        <v>-0.1588</v>
       </c>
       <c r="T16" t="n">
-        <v>0.244</v>
+        <v>-0.7053</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.5465</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.3573</v>
+        <v>2.5359</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2402</v>
+        <v>2.3573</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.5975</v>
+        <v>0.1787</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. STUTZ</t>
+          <t>M. ANDREATTA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9797</v>
+        <v>3.0807</v>
       </c>
       <c r="E17" t="n">
-        <v>4.3862</v>
+        <v>4.2767</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4065</v>
+        <v>-1.196</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1299</v>
+        <v>3.4368</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4426</v>
+        <v>1.2976</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.3128</v>
+        <v>2.1392</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9701</v>
+        <v>3.5833</v>
       </c>
       <c r="K17" t="n">
-        <v>2.826</v>
+        <v>1.7943</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1441</v>
+        <v>1.789</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.8402</v>
+        <v>-0.1465</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3833</v>
+        <v>-0.4967</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.4569</v>
+        <v>0.3502</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5075</v>
+        <v>0.9745</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9145</v>
+        <v>0.4532</v>
       </c>
       <c r="U17" t="n">
-        <v>0.407</v>
+        <v>0.5213</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5359</v>
+        <v>-2.3573</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3573</v>
+        <v>0.2402</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1787</v>
+        <v>-2.5975</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K.  BAOKO</t>
+          <t>J. FANER CATALA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4023</v>
+        <v>-0.6693</v>
       </c>
       <c r="E19" t="n">
-        <v>0.247</v>
+        <v>0.1348</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6493</v>
+        <v>-0.8041</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6197</v>
+        <v>-0.8368</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7722</v>
+        <v>1.9496</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1525</v>
+        <v>-2.7864</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2114</v>
+        <v>0.9198</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1324</v>
+        <v>2.2225</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0789</v>
+        <v>-1.3027</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5917</v>
+        <v>-1.7566</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3602</v>
+        <v>-0.2729</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2314</v>
+        <v>-1.4836</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7521</v>
+        <v>0.2209</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4997</v>
+        <v>-0.0621</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2523</v>
+        <v>0.283</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7207</v>
+        <v>1.1786</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5893</v>
+        <v>2.3573</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.31</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. FANER CATALA</t>
+          <t>K.  BAOKO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6875</v>
+        <v>-1.9481</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3882</v>
+        <v>-0.1714</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2993</v>
+        <v>-1.7766</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8368</v>
+        <v>0.6197</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9496</v>
+        <v>0.7722</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.7864</v>
+        <v>-0.1525</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9198</v>
+        <v>1.2114</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2225</v>
+        <v>1.1324</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3027</v>
+        <v>0.0789</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7566</v>
+        <v>-0.5917</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2729</v>
+        <v>-0.3602</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4836</v>
+        <v>-0.2314</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8481</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7973</v>
+        <v>0.2064</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5851</v>
+        <v>0.0813</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2122</v>
+        <v>0.125</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1786</v>
+        <v>-0.7207</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3573</v>
+        <v>0.5893</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1786</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8423</v>
+        <v>-2.9922</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1281</v>
+        <v>-1.3373</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7142</v>
+        <v>-1.6549</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6919</v>
@@ -2092,13 +2092,13 @@
         <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4657</v>
+        <v>0.3157</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3757</v>
+        <v>0.1665</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.1492</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7514</v>
+        <v>-3.9623</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.3341</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.5039</v>
+        <v>-4.2965</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2205</v>
@@ -2170,13 +2170,13 @@
         <v>1.8481</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4013</v>
+        <v>1.1904</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0808</v>
+        <v>0.6624</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3205</v>
+        <v>0.528</v>
       </c>
       <c r="V22" t="n">
         <v>-4.7536</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>12.3487</v>
+        <v>13.0461</v>
       </c>
       <c r="E23" t="n">
-        <v>25.4838</v>
+        <v>25.4839</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.1349</v>
+        <v>-12.4376</v>
       </c>
       <c r="G23" t="n">
         <v>2.8816</v>
@@ -2239,7 +2239,7 @@
         <v>-13.7978</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0534</v>
+        <v>-2.053399999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-14.3738</v>
@@ -2248,13 +2248,13 @@
         <v>12.3205</v>
       </c>
       <c r="S23" t="n">
-        <v>3.9909</v>
+        <v>4.6884</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7156</v>
+        <v>0.7155999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>3.2751</v>
+        <v>3.9726</v>
       </c>
       <c r="V23" t="n">
         <v>7.529599999999999</v>
